--- a/Documentación/Carta Gantt.xlsx
+++ b/Documentación/Carta Gantt.xlsx
@@ -294,7 +294,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,12 +341,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2DBDB"/>
         <bgColor rgb="FFF2DBDB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF9900"/>
-        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
     <fill>
@@ -614,7 +608,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="100">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -794,85 +788,81 @@
     <xf borderId="20" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="21" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="17" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="9" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="23" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="14" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="15" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="15" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="15" fillId="9" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="15" fillId="9" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="15" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="15" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="10" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="10" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="15" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="11" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="11" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="12" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="15" fillId="12" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="12" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="12" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="12" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="13" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="13" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="15" fillId="13" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="15" fillId="13" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="13" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="15" fillId="13" fontId="15" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="13" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="14" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="14" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="13" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="14" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="14" fontId="15" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="14" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="14" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="14" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="13" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="20" fillId="14" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="20" fillId="13" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="14" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="13" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2892,7 +2882,7 @@
         <v>22</v>
       </c>
       <c r="D15" s="60">
-        <v>0.8</v>
+        <v>1.0</v>
       </c>
       <c r="E15" s="61">
         <f t="shared" si="5"/>
@@ -2940,12 +2930,12 @@
       <c r="AM15" s="64"/>
       <c r="AN15" s="64"/>
       <c r="AO15" s="64"/>
-      <c r="AP15" s="69"/>
-      <c r="AQ15" s="70"/>
-      <c r="AR15" s="71"/>
-      <c r="AS15" s="71"/>
-      <c r="AT15" s="71"/>
-      <c r="AU15" s="71"/>
+      <c r="AP15" s="64"/>
+      <c r="AQ15" s="69"/>
+      <c r="AR15" s="70"/>
+      <c r="AS15" s="70"/>
+      <c r="AT15" s="70"/>
+      <c r="AU15" s="70"/>
       <c r="AV15" s="33"/>
       <c r="AW15" s="33"/>
       <c r="AX15" s="33"/>
@@ -2999,13 +2989,13 @@
       <c r="A16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="72" t="s">
+      <c r="B16" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="73"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="75"/>
-      <c r="F16" s="75"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
       <c r="G16" s="39"/>
       <c r="H16" s="39" t="str">
         <f>IF(OR(ISBLANK('Casa Taller Muso'!task_start),ISBLANK('Casa Taller Muso'!task_end)),"",'Casa Taller Muso'!task_end-'Casa Taller Muso'!task_start+1)</f>
@@ -3049,8 +3039,8 @@
       <c r="AR16" s="68"/>
       <c r="AS16" s="68"/>
       <c r="AT16" s="68"/>
-      <c r="AU16" s="71"/>
-      <c r="AV16" s="71"/>
+      <c r="AU16" s="70"/>
+      <c r="AV16" s="70"/>
       <c r="AW16" s="33"/>
       <c r="AX16" s="33"/>
       <c r="AY16" s="33"/>
@@ -3101,20 +3091,20 @@
     </row>
     <row r="17" ht="30.0" customHeight="1">
       <c r="A17" s="8"/>
-      <c r="B17" s="76" t="s">
+      <c r="B17" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="77" t="s">
+      <c r="C17" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="78">
+      <c r="D17" s="77">
         <v>1.0</v>
       </c>
-      <c r="E17" s="79">
+      <c r="E17" s="78">
         <f>F15+2</f>
         <v>46139</v>
       </c>
-      <c r="F17" s="79">
+      <c r="F17" s="78">
         <f>E17+2</f>
         <v>46141</v>
       </c>
@@ -3213,20 +3203,20 @@
     </row>
     <row r="18" ht="30.0" customHeight="1">
       <c r="A18" s="8"/>
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="77" t="s">
+      <c r="C18" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="78">
-        <v>0.4</v>
-      </c>
-      <c r="E18" s="79">
+      <c r="D18" s="77">
+        <v>1.0</v>
+      </c>
+      <c r="E18" s="78">
         <f>F17-1</f>
         <v>46140</v>
       </c>
-      <c r="F18" s="79">
+      <c r="F18" s="78">
         <f>E18+14</f>
         <v>46154</v>
       </c>
@@ -3278,14 +3268,14 @@
       <c r="AW18" s="46"/>
       <c r="AX18" s="46"/>
       <c r="AY18" s="46"/>
-      <c r="AZ18" s="80"/>
-      <c r="BA18" s="80"/>
-      <c r="BB18" s="80"/>
-      <c r="BC18" s="80"/>
-      <c r="BD18" s="80"/>
-      <c r="BE18" s="80"/>
-      <c r="BF18" s="80"/>
-      <c r="BG18" s="80"/>
+      <c r="AZ18" s="46"/>
+      <c r="BA18" s="46"/>
+      <c r="BB18" s="46"/>
+      <c r="BC18" s="46"/>
+      <c r="BD18" s="46"/>
+      <c r="BE18" s="46"/>
+      <c r="BF18" s="46"/>
+      <c r="BG18" s="46"/>
       <c r="BH18" s="48"/>
       <c r="BI18" s="40"/>
       <c r="BJ18" s="40"/>
@@ -3325,20 +3315,20 @@
     </row>
     <row r="19" ht="30.0" customHeight="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="78">
-        <v>0.8</v>
-      </c>
-      <c r="E19" s="79">
+      <c r="D19" s="77">
+        <v>1.0</v>
+      </c>
+      <c r="E19" s="78">
         <f>F18</f>
         <v>46154</v>
       </c>
-      <c r="F19" s="79">
+      <c r="F19" s="78">
         <f>E19+10</f>
         <v>46164</v>
       </c>
@@ -3381,8 +3371,8 @@
       <c r="AN19" s="49"/>
       <c r="AO19" s="49"/>
       <c r="AP19" s="33"/>
-      <c r="AQ19" s="71"/>
-      <c r="AR19" s="71"/>
+      <c r="AQ19" s="70"/>
+      <c r="AR19" s="70"/>
       <c r="AS19" s="66"/>
       <c r="AT19" s="66"/>
       <c r="AU19" s="66"/>
@@ -3406,8 +3396,8 @@
       <c r="BM19" s="46"/>
       <c r="BN19" s="46"/>
       <c r="BO19" s="46"/>
-      <c r="BP19" s="80"/>
-      <c r="BQ19" s="80"/>
+      <c r="BP19" s="46"/>
+      <c r="BQ19" s="46"/>
       <c r="BR19" s="52"/>
       <c r="BS19" s="33"/>
       <c r="BT19" s="40"/>
@@ -3437,20 +3427,20 @@
     </row>
     <row r="20" ht="30.0" customHeight="1">
       <c r="A20" s="8"/>
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="77" t="s">
+      <c r="C20" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="78">
-        <v>0.2</v>
-      </c>
-      <c r="E20" s="79">
+      <c r="D20" s="77">
+        <v>1.0</v>
+      </c>
+      <c r="E20" s="78">
         <f>F19+3</f>
         <v>46167</v>
       </c>
-      <c r="F20" s="79">
+      <c r="F20" s="78">
         <f>E20+8</f>
         <v>46175</v>
       </c>
@@ -3524,13 +3514,13 @@
       <c r="BS20" s="45"/>
       <c r="BT20" s="46"/>
       <c r="BU20" s="46"/>
-      <c r="BV20" s="80"/>
-      <c r="BW20" s="80"/>
-      <c r="BX20" s="80"/>
-      <c r="BY20" s="80"/>
-      <c r="BZ20" s="80"/>
-      <c r="CA20" s="80"/>
-      <c r="CB20" s="80"/>
+      <c r="BV20" s="46"/>
+      <c r="BW20" s="46"/>
+      <c r="BX20" s="46"/>
+      <c r="BY20" s="46"/>
+      <c r="BZ20" s="46"/>
+      <c r="CA20" s="46"/>
+      <c r="CB20" s="46"/>
       <c r="CC20" s="48"/>
       <c r="CD20" s="40"/>
       <c r="CE20" s="40"/>
@@ -3551,13 +3541,13 @@
       <c r="A21" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="81" t="s">
+      <c r="B21" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="82"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="84"/>
-      <c r="F21" s="84"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="82"/>
       <c r="G21" s="39"/>
       <c r="H21" s="39" t="str">
         <f>IF(OR(ISBLANK('Casa Taller Muso'!task_start),ISBLANK('Casa Taller Muso'!task_end)),"",'Casa Taller Muso'!task_end-'Casa Taller Muso'!task_start+1)</f>
@@ -3653,20 +3643,20 @@
     </row>
     <row r="22" ht="30.0" customHeight="1">
       <c r="A22" s="8"/>
-      <c r="B22" s="85" t="s">
+      <c r="B22" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="86" t="s">
+      <c r="C22" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="87">
-        <v>0.0</v>
-      </c>
-      <c r="E22" s="88">
+      <c r="D22" s="85">
+        <v>1.0</v>
+      </c>
+      <c r="E22" s="86">
         <f>F20+1</f>
         <v>46176</v>
       </c>
-      <c r="F22" s="88">
+      <c r="F22" s="86">
         <f>E22+4</f>
         <v>46180</v>
       </c>
@@ -3747,11 +3737,11 @@
       <c r="BZ22" s="33"/>
       <c r="CA22" s="33"/>
       <c r="CB22" s="45"/>
-      <c r="CC22" s="80"/>
-      <c r="CD22" s="80"/>
-      <c r="CE22" s="80"/>
-      <c r="CF22" s="80"/>
-      <c r="CG22" s="80"/>
+      <c r="CC22" s="46"/>
+      <c r="CD22" s="46"/>
+      <c r="CE22" s="46"/>
+      <c r="CF22" s="46"/>
+      <c r="CG22" s="46"/>
       <c r="CH22" s="48"/>
       <c r="CI22" s="40"/>
       <c r="CJ22" s="40"/>
@@ -3765,20 +3755,20 @@
     </row>
     <row r="23" ht="30.0" customHeight="1">
       <c r="A23" s="8"/>
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="86" t="s">
+      <c r="C23" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="87">
-        <v>0.0</v>
-      </c>
-      <c r="E23" s="88">
+      <c r="D23" s="85">
+        <v>1.0</v>
+      </c>
+      <c r="E23" s="86">
         <f>F22</f>
         <v>46180</v>
       </c>
-      <c r="F23" s="88">
+      <c r="F23" s="86">
         <f t="shared" ref="F23:F24" si="6">E23+3</f>
         <v>46183</v>
       </c>
@@ -3863,10 +3853,10 @@
       <c r="CD23" s="49"/>
       <c r="CE23" s="49"/>
       <c r="CF23" s="50"/>
-      <c r="CG23" s="80"/>
-      <c r="CH23" s="80"/>
-      <c r="CI23" s="80"/>
-      <c r="CJ23" s="80"/>
+      <c r="CG23" s="46"/>
+      <c r="CH23" s="46"/>
+      <c r="CI23" s="46"/>
+      <c r="CJ23" s="46"/>
       <c r="CK23" s="48"/>
       <c r="CL23" s="40"/>
       <c r="CM23" s="40"/>
@@ -3877,20 +3867,20 @@
     </row>
     <row r="24" ht="30.0" customHeight="1">
       <c r="A24" s="8"/>
-      <c r="B24" s="85" t="s">
+      <c r="B24" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="86" t="s">
+      <c r="C24" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="87">
-        <v>0.0</v>
-      </c>
-      <c r="E24" s="88">
+      <c r="D24" s="85">
+        <v>1.0</v>
+      </c>
+      <c r="E24" s="86">
         <f>F23+1</f>
         <v>46184</v>
       </c>
-      <c r="F24" s="88">
+      <c r="F24" s="86">
         <f t="shared" si="6"/>
         <v>46187</v>
       </c>
@@ -3979,10 +3969,10 @@
       <c r="CH24" s="49"/>
       <c r="CI24" s="49"/>
       <c r="CJ24" s="50"/>
-      <c r="CK24" s="80"/>
-      <c r="CL24" s="80"/>
-      <c r="CM24" s="80"/>
-      <c r="CN24" s="80"/>
+      <c r="CK24" s="46"/>
+      <c r="CL24" s="46"/>
+      <c r="CM24" s="46"/>
+      <c r="CN24" s="46"/>
       <c r="CO24" s="34"/>
       <c r="CP24" s="34"/>
       <c r="CQ24" s="34"/>
@@ -3991,120 +3981,120 @@
       <c r="A25" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="89" t="s">
+      <c r="B25" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="90"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="93"/>
-      <c r="G25" s="94"/>
-      <c r="H25" s="94" t="str">
+      <c r="C25" s="88"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="90"/>
+      <c r="F25" s="91"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="92" t="str">
         <f>IF(OR(ISBLANK('Casa Taller Muso'!task_start),ISBLANK('Casa Taller Muso'!task_end)),"",'Casa Taller Muso'!task_end-'Casa Taller Muso'!task_start+1)</f>
         <v/>
       </c>
-      <c r="I25" s="95"/>
-      <c r="J25" s="95"/>
-      <c r="K25" s="95"/>
-      <c r="L25" s="95"/>
-      <c r="M25" s="95"/>
-      <c r="N25" s="95"/>
-      <c r="O25" s="95"/>
-      <c r="P25" s="95"/>
-      <c r="Q25" s="95"/>
-      <c r="R25" s="95"/>
-      <c r="S25" s="95"/>
-      <c r="T25" s="95"/>
-      <c r="U25" s="95"/>
-      <c r="V25" s="95"/>
-      <c r="W25" s="95"/>
-      <c r="X25" s="95"/>
-      <c r="Y25" s="95"/>
-      <c r="Z25" s="95"/>
-      <c r="AA25" s="95"/>
-      <c r="AB25" s="95"/>
-      <c r="AC25" s="95"/>
-      <c r="AD25" s="95"/>
-      <c r="AE25" s="95"/>
-      <c r="AF25" s="95"/>
-      <c r="AG25" s="95"/>
-      <c r="AH25" s="95"/>
-      <c r="AI25" s="95"/>
-      <c r="AJ25" s="95"/>
-      <c r="AK25" s="95"/>
-      <c r="AL25" s="95"/>
-      <c r="AM25" s="95"/>
-      <c r="AN25" s="95"/>
-      <c r="AO25" s="95"/>
-      <c r="AP25" s="95"/>
-      <c r="AQ25" s="95"/>
-      <c r="AR25" s="95"/>
-      <c r="AS25" s="95"/>
-      <c r="AT25" s="95"/>
-      <c r="AU25" s="95"/>
-      <c r="AV25" s="95"/>
-      <c r="AW25" s="95"/>
-      <c r="AX25" s="95"/>
-      <c r="AY25" s="95"/>
-      <c r="AZ25" s="95"/>
-      <c r="BA25" s="95"/>
-      <c r="BB25" s="95"/>
-      <c r="BC25" s="95"/>
-      <c r="BD25" s="95"/>
-      <c r="BE25" s="95"/>
-      <c r="BF25" s="95"/>
-      <c r="BG25" s="95"/>
-      <c r="BH25" s="95"/>
-      <c r="BI25" s="95"/>
-      <c r="BJ25" s="95"/>
-      <c r="BK25" s="95"/>
-      <c r="BL25" s="95"/>
-      <c r="BM25" s="95"/>
-      <c r="BN25" s="96"/>
-      <c r="BO25" s="96"/>
-      <c r="BP25" s="96"/>
-      <c r="BQ25" s="96"/>
-      <c r="BR25" s="96"/>
-      <c r="BS25" s="96"/>
-      <c r="BT25" s="95"/>
-      <c r="BU25" s="95"/>
-      <c r="BV25" s="95"/>
-      <c r="BW25" s="96"/>
-      <c r="BX25" s="96"/>
-      <c r="BY25" s="96"/>
-      <c r="BZ25" s="96"/>
-      <c r="CA25" s="96"/>
-      <c r="CB25" s="96"/>
-      <c r="CC25" s="95"/>
-      <c r="CD25" s="95"/>
-      <c r="CE25" s="95"/>
-      <c r="CF25" s="95"/>
-      <c r="CG25" s="95"/>
-      <c r="CH25" s="95"/>
-      <c r="CI25" s="95"/>
-      <c r="CJ25" s="95"/>
-      <c r="CK25" s="96"/>
-      <c r="CL25" s="96"/>
-      <c r="CM25" s="96"/>
-      <c r="CN25" s="96"/>
-      <c r="CO25" s="97"/>
-      <c r="CP25" s="97"/>
-      <c r="CQ25" s="97"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="93"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="93"/>
+      <c r="N25" s="93"/>
+      <c r="O25" s="93"/>
+      <c r="P25" s="93"/>
+      <c r="Q25" s="93"/>
+      <c r="R25" s="93"/>
+      <c r="S25" s="93"/>
+      <c r="T25" s="93"/>
+      <c r="U25" s="93"/>
+      <c r="V25" s="93"/>
+      <c r="W25" s="93"/>
+      <c r="X25" s="93"/>
+      <c r="Y25" s="93"/>
+      <c r="Z25" s="93"/>
+      <c r="AA25" s="93"/>
+      <c r="AB25" s="93"/>
+      <c r="AC25" s="93"/>
+      <c r="AD25" s="93"/>
+      <c r="AE25" s="93"/>
+      <c r="AF25" s="93"/>
+      <c r="AG25" s="93"/>
+      <c r="AH25" s="93"/>
+      <c r="AI25" s="93"/>
+      <c r="AJ25" s="93"/>
+      <c r="AK25" s="93"/>
+      <c r="AL25" s="93"/>
+      <c r="AM25" s="93"/>
+      <c r="AN25" s="93"/>
+      <c r="AO25" s="93"/>
+      <c r="AP25" s="93"/>
+      <c r="AQ25" s="93"/>
+      <c r="AR25" s="93"/>
+      <c r="AS25" s="93"/>
+      <c r="AT25" s="93"/>
+      <c r="AU25" s="93"/>
+      <c r="AV25" s="93"/>
+      <c r="AW25" s="93"/>
+      <c r="AX25" s="93"/>
+      <c r="AY25" s="93"/>
+      <c r="AZ25" s="93"/>
+      <c r="BA25" s="93"/>
+      <c r="BB25" s="93"/>
+      <c r="BC25" s="93"/>
+      <c r="BD25" s="93"/>
+      <c r="BE25" s="93"/>
+      <c r="BF25" s="93"/>
+      <c r="BG25" s="93"/>
+      <c r="BH25" s="93"/>
+      <c r="BI25" s="93"/>
+      <c r="BJ25" s="93"/>
+      <c r="BK25" s="93"/>
+      <c r="BL25" s="93"/>
+      <c r="BM25" s="93"/>
+      <c r="BN25" s="94"/>
+      <c r="BO25" s="94"/>
+      <c r="BP25" s="94"/>
+      <c r="BQ25" s="94"/>
+      <c r="BR25" s="94"/>
+      <c r="BS25" s="94"/>
+      <c r="BT25" s="93"/>
+      <c r="BU25" s="93"/>
+      <c r="BV25" s="93"/>
+      <c r="BW25" s="94"/>
+      <c r="BX25" s="94"/>
+      <c r="BY25" s="94"/>
+      <c r="BZ25" s="94"/>
+      <c r="CA25" s="94"/>
+      <c r="CB25" s="94"/>
+      <c r="CC25" s="93"/>
+      <c r="CD25" s="93"/>
+      <c r="CE25" s="93"/>
+      <c r="CF25" s="93"/>
+      <c r="CG25" s="93"/>
+      <c r="CH25" s="93"/>
+      <c r="CI25" s="93"/>
+      <c r="CJ25" s="93"/>
+      <c r="CK25" s="94"/>
+      <c r="CL25" s="94"/>
+      <c r="CM25" s="94"/>
+      <c r="CN25" s="94"/>
+      <c r="CO25" s="95"/>
+      <c r="CP25" s="95"/>
+      <c r="CQ25" s="95"/>
     </row>
     <row r="26" ht="30.0" customHeight="1">
       <c r="A26" s="8"/>
       <c r="E26" s="10"/>
-      <c r="G26" s="98"/>
+      <c r="G26" s="96"/>
     </row>
     <row r="27" ht="30.0" customHeight="1">
       <c r="A27" s="8"/>
-      <c r="C27" s="99"/>
+      <c r="C27" s="97"/>
       <c r="E27" s="10"/>
-      <c r="F27" s="100"/>
+      <c r="F27" s="98"/>
     </row>
     <row r="28" ht="30.0" customHeight="1">
       <c r="A28" s="8"/>
-      <c r="C28" s="101"/>
+      <c r="C28" s="99"/>
       <c r="E28" s="10"/>
     </row>
     <row r="29" ht="30.0" customHeight="1">
